--- a/docs/方案与报价/爱对-报价单.xlsx
+++ b/docs/方案与报价/爱对-报价单.xlsx
@@ -1468,18 +1468,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>7.1 回归测试与单元测试</t>
+          <t>7.1 回归测试与质量验收</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>使用真实抖音账单跑回归，64+ 单元测试覆盖核心引擎</t>
+          <t>使用真实抖音账单做回归测试，覆盖核心对账与利润核算流程</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
           <t>价值：保障对账准确性 ≥ 95%
-流程：测试 → 修 bug → 复测</t>
+流程：测试 → 修正 → 复测</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
@@ -1498,12 +1498,12 @@
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>7.2 部署上线</t>
+          <t>7.2 上线部署</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>部署到客户指定环境（GitHub Pages / 内部服务器 / 私有 OSS），配置域名与 HTTPS</t>
+          <t>部署到客户指定环境（公网域名或内部服务器均可），配置域名访问</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1613,14 +1613,14 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>采用纯前端 React 方案，浏览器端解析 Excel + localStorage 持久化，零后端依赖，开箱即用。</t>
+          <t>系统采用浏览器端纯 Web 方案，财务无需安装任何软件，打开网页即可使用。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>11 个平台（7 国内 + 4 海外）通过适配器模式统一处理，新增平台仅需 1 个映射文件，扩展性强。</t>
+          <t>11 个平台（7 国内 + 4 海外）统一管理，新增平台扩展灵活。</t>
         </is>
       </c>
     </row>
@@ -1718,42 +1718,42 @@
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>🔧 技术栈</t>
+          <t>🔧 系统说明</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>• 前端：React 19 + Vite 8 + lucide-react</t>
+          <t>• 浏览器端纯 Web 系统，无需安装任何客户端</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="17" t="inlineStr">
         <is>
-          <t>• Excel 解析与生成：SheetJS (xlsx)</t>
+          <t>• 支持 Chrome / Edge 等主流浏览器</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>• 状态管理：自研 Hook（useReducer + localStorage）</t>
+          <t>• 数据保存在客户自有环境，不上传第三方服务</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="17" t="inlineStr">
         <is>
-          <t>• 测试：vitest（64+ 单元测试，覆盖核心引擎）</t>
+          <t>• 支持上线到客户指定地址（公网域名 / 内部服务器均可）</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>• 部署：纯静态资源，支持任意 CDN/Pages 服务</t>
+          <t>• 满足客户《系统初稿模板5.22》全部表头规范</t>
         </is>
       </c>
     </row>
@@ -1767,14 +1767,14 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>• 完整源代码（Git 仓库 + 提交历史）</t>
+          <t>• 完整系统（含历史变更记录可追溯）</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>• 生产构建包（dist 目录）+ 部署文档</t>
+          <t>• 上线就绪的可执行版本 + 上线说明文档</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>• 开发者扩展指南（新增平台/报表/字段）</t>
+          <t>• 系统扩展指南（新增平台/报表/字段）</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t>• 客户需要在第 1 周提供 3-5 个真实账单样本以提前调试适配器</t>
+          <t>• 客户需要在第 1 周提供 3-5 个真实账单样本以提前调试适配</t>
         </is>
       </c>
     </row>
@@ -1879,14 +1879,14 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="17" t="inlineStr">
         <is>
-          <t>• 数据存储默认 localStorage（5MB 配额），如需更大或多端同步需追加后端 API</t>
+          <t>• 数据存储默认浏览器本地，如需多端同步需追加服务端能力（单独评估）</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>• 角色/权限/备份目前为前端展示，生产级权限控制需后端配套</t>
+          <t>• 角色/权限/备份目前为前端展示，生产级权限控制需服务端配套</t>
         </is>
       </c>
     </row>
